--- a/Sales_Performance_Dashboard.xlsx
+++ b/Sales_Performance_Dashboard.xlsx
@@ -5,23 +5,38 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9b72b7b7d68c99e8/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9b72b7b7d68c99e8/Desktop/Sales Performance Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="398" documentId="8_{12607A60-FA04-47D3-8647-9380F13D8899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{695B1958-E522-4ABF-BAF4-F99EBE8BA4D4}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="8_{229786EF-41AE-4622-9C49-C04738406AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E222ACF7-B079-4E51-BD6C-DEA89866D096}"/>
   <bookViews>
-    <workbookView xWindow="11508" yWindow="0" windowWidth="11148" windowHeight="13776" firstSheet="1" activeTab="2" xr2:uid="{A853B77B-0601-4C28-9F7C-E7BEB5BA7DF5}"/>
+    <workbookView xWindow="11508" yWindow="12" windowWidth="11148" windowHeight="9960" firstSheet="1" activeTab="1" xr2:uid="{A853B77B-0601-4C28-9F7C-E7BEB5BA7DF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Data" sheetId="1" r:id="rId1"/>
     <sheet name="Dashboard" sheetId="3" r:id="rId2"/>
     <sheet name="Pivot Tables" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_Category">#N/A</definedName>
+    <definedName name="Slicer_Location">#N/A</definedName>
+    <definedName name="Slicer_Product">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId5"/>
+        <x14:slicerCache r:id="rId6"/>
+        <x14:slicerCache r:id="rId7"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -280,9 +295,6 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Pivot Tables</t>
-  </si>
-  <si>
     <t>Revenue by Location</t>
   </si>
   <si>
@@ -294,17 +306,21 @@
   <si>
     <t>Profit by Location</t>
   </si>
+  <si>
+    <t xml:space="preserve"> PIVOT TABLES - SALES ANALYST</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="167" formatCode="000,000"/>
-    <numFmt numFmtId="168" formatCode="#,000"/>
-    <numFmt numFmtId="169" formatCode="#,#00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="000,000"/>
+    <numFmt numFmtId="165" formatCode="#,000"/>
+    <numFmt numFmtId="166" formatCode="#,#00"/>
+    <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +352,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -357,14 +381,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -381,23 +399,1139 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="208">
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ "/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -424,8 +1558,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Sales Data Project.xlsx]Pivot Tables!PivotTable1</c:name>
-    <c:fmtId val="8"/>
+    <c:name>[Sales_Performance_Dashboard.xlsx]Pivot Tables!Revenue by Location</c:name>
+    <c:fmtId val="25"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -533,21 +1667,21 @@
           <a:gradFill rotWithShape="1">
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent6">
                   <a:satMod val="103000"/>
                   <a:lumMod val="102000"/>
                   <a:tint val="94000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="50000">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent6">
                   <a:satMod val="110000"/>
                   <a:lumMod val="100000"/>
                   <a:shade val="100000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="100000">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent6">
                   <a:lumMod val="99000"/>
                   <a:satMod val="120000"/>
                   <a:shade val="78000"/>
@@ -568,49 +1702,177 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
           <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -679,21 +1941,21 @@
             <a:gradFill rotWithShape="1">
               <a:gsLst>
                 <a:gs pos="0">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent6">
                     <a:satMod val="103000"/>
                     <a:lumMod val="102000"/>
                     <a:tint val="94000"/>
                   </a:schemeClr>
                 </a:gs>
                 <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent6">
                     <a:satMod val="110000"/>
                     <a:lumMod val="100000"/>
                     <a:shade val="100000"/>
                   </a:schemeClr>
                 </a:gs>
                 <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent6">
                     <a:lumMod val="99000"/>
                     <a:satMod val="120000"/>
                     <a:shade val="78000"/>
@@ -800,7 +2062,7 @@
             <c:numRef>
               <c:f>'Pivot Tables'!$B$6:$B$12</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * "-"_ ;_ @_ </c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1249000</c:v>
@@ -825,7 +2087,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E785-400A-994E-5BF7253DBEC2}"/>
+              <c16:uniqueId val="{00000000-1061-47D8-9E58-C930EC4A1787}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -914,7 +2176,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1070,8 +2332,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Sales Data Project.xlsx]Pivot Tables!PivotTable2</c:name>
-    <c:fmtId val="6"/>
+    <c:name>[Sales_Performance_Dashboard.xlsx]Pivot Tables!Revenue by Product</c:name>
+    <c:fmtId val="19"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1179,21 +2441,21 @@
           <a:gradFill rotWithShape="1">
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent6">
                   <a:satMod val="103000"/>
                   <a:lumMod val="102000"/>
                   <a:tint val="94000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="50000">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent6">
                   <a:satMod val="110000"/>
                   <a:lumMod val="100000"/>
                   <a:shade val="100000"/>
                 </a:schemeClr>
               </a:gs>
               <a:gs pos="100000">
-                <a:schemeClr val="accent1">
+                <a:schemeClr val="accent6">
                   <a:lumMod val="99000"/>
                   <a:satMod val="120000"/>
                   <a:shade val="78000"/>
@@ -1214,49 +2476,177 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
           <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent6">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1325,21 +2715,21 @@
             <a:gradFill rotWithShape="1">
               <a:gsLst>
                 <a:gs pos="0">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent6">
                     <a:satMod val="103000"/>
                     <a:lumMod val="102000"/>
                     <a:tint val="94000"/>
                   </a:schemeClr>
                 </a:gs>
                 <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent6">
                     <a:satMod val="110000"/>
                     <a:lumMod val="100000"/>
                     <a:shade val="100000"/>
                   </a:schemeClr>
                 </a:gs>
                 <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
+                  <a:schemeClr val="accent6">
                     <a:lumMod val="99000"/>
                     <a:satMod val="120000"/>
                     <a:shade val="78000"/>
@@ -1440,7 +2830,7 @@
             <c:numRef>
               <c:f>'Pivot Tables'!$B$18:$B$22</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * "-"_ ;_ @_ </c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>289500</c:v>
@@ -1459,7 +2849,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-36CB-42E1-A34B-544CB5F1170D}"/>
+              <c16:uniqueId val="{00000000-AB51-4B65-B462-5865D514B389}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1548,7 +2938,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1704,8 +3094,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Sales Data Project.xlsx]Pivot Tables!PivotTable3</c:name>
-    <c:fmtId val="3"/>
+    <c:name>[Sales_Performance_Dashboard.xlsx]Pivot Tables!Profit by Location</c:name>
+    <c:fmtId val="18"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -1853,49 +3243,177 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
           <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2085,7 +3603,7 @@
             <c:numRef>
               <c:f>'Pivot Tables'!$B$28:$B$34</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * "-"_ ;_ @_ </c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>192300</c:v>
@@ -2110,7 +3628,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EE66-4F2B-AADF-4D8EE4351C86}"/>
+              <c16:uniqueId val="{00000000-327C-49CA-A685-1B6FEBABD6B2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2199,7 +3717,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2355,8 +3873,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Sales Data Project.xlsx]Pivot Tables!PivotTable4</c:name>
-    <c:fmtId val="6"/>
+    <c:name>[Sales_Performance_Dashboard.xlsx]Pivot Tables!Daily Revenue Trend</c:name>
+    <c:fmtId val="22"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -2499,27 +4017,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="4"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst>
-              <a:glow rad="63500">
-                <a:schemeClr val="accent2">
-                  <a:satMod val="175000"/>
-                  <a:alpha val="25000"/>
-                </a:schemeClr>
-              </a:glow>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2551,7 +4049,132 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent2">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:miter lim="800000"/>
+          </a:ln>
+          <a:effectLst>
+            <a:glow rad="63500">
+              <a:schemeClr val="accent2">
+                <a:satMod val="175000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:glow>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2758,7 +4381,7 @@
             <c:numRef>
               <c:f>'Pivot Tables'!$E$6:$E$54</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * "-"_ ;_ @_ </c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
                   <c:v>250000</c:v>
@@ -2909,12 +4532,11 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3528-496D-9CE5-46933042EA3D}"/>
+              <c16:uniqueId val="{00000000-62E4-4627-AAF1-5AD8D403C618}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3028,7 +4650,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="_ [$₹-449]\ * #,##0_ ;_ [$₹-449]\ * \-#,##0_ ;_ [$₹-449]\ * &quot;-&quot;_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3164,13 +4786,10 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -3204,13 +4823,10 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -5329,21 +6945,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>445697</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>31315</xdr:rowOff>
+      <xdr:colOff>167899</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>31316</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 8">
+        <xdr:cNvPr id="13" name="Chart 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7D5BF52-7155-4987-9F87-26EFBE97A2D6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1611C069-1338-4390-9C92-6B27DCF8D4CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5366,22 +6982,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>281976</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:colOff>142068</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>136078</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>29489</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>29490</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="10" name="Chart 9">
+        <xdr:cNvPr id="14" name="Chart 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29127553-F70D-4C0C-806A-0F240F01A504}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96266D71-28E8-43A9-A322-56D287345F6B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5405,21 +7021,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>431319</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>19833</xdr:rowOff>
+      <xdr:colOff>232475</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>19834</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="11" name="Chart 10">
+        <xdr:cNvPr id="15" name="Chart 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AC7361B-FCFD-4AE5-8239-CD6254301D93}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B523D1EF-9342-4DB2-96A9-C9D3AFF25BBB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5442,22 +7058,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>296532</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>174625</xdr:rowOff>
+      <xdr:colOff>180814</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>174626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>15875</xdr:rowOff>
+      <xdr:colOff>127001</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>15876</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="12" name="Chart 11">
+        <xdr:cNvPr id="16" name="Chart 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13E374CA-F113-4022-9F04-445233FBDF14}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC0B8848-AB5D-4B0C-BF3E-21D447F287C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5475,6 +7091,479 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>90874</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>35719</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="17" name="Product 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{432CACAF-5F75-43A2-9D5B-8CD29DBDAB42}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Product 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="1658471"/>
+              <a:ext cx="1794168" cy="1470072"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>970768</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>356522</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="18" name="Category 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA7084D9-E109-47E9-BB6B-0EA9D60AFFDF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Category 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3973944" y="1658471"/>
+              <a:ext cx="1828637" cy="991720"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>750093</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>743144</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>164968</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="19" name="Location 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98D2AC29-CB79-442A-8F5D-E797C214357E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Location 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8078740" y="1645863"/>
+              <a:ext cx="1808404" cy="2149811"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>22013</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>138007</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9313</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Location">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1173249A-6432-1AF2-89DF-1D88B5EEAA74}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Location"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8190653" y="4283287"/>
+              <a:ext cx="1816100" cy="2010833"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>22861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>167641</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Category">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD4205F5-BA76-307D-8184-9C7A9328648D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Category"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8176260" y="2842261"/>
+              <a:ext cx="1828800" cy="922020"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>220981</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>15241</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Product">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A753C33-783F-A483-8C51-2979FD580046}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Product"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8191500" y="800101"/>
+              <a:ext cx="1828800" cy="1485900"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5547,7 +7636,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="Electronics"/>
+        <s v="Accessories"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Location" numFmtId="0">
       <sharedItems count="6">
@@ -5563,7 +7655,35 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Units Sold" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="30"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="30" count="27">
+        <n v="5"/>
+        <n v="20"/>
+        <n v="15"/>
+        <n v="8"/>
+        <n v="3"/>
+        <n v="25"/>
+        <n v="18"/>
+        <n v="6"/>
+        <n v="4"/>
+        <n v="30"/>
+        <n v="12"/>
+        <n v="10"/>
+        <n v="7"/>
+        <n v="22"/>
+        <n v="16"/>
+        <n v="9"/>
+        <n v="28"/>
+        <n v="14"/>
+        <n v="24"/>
+        <n v="19"/>
+        <n v="26"/>
+        <n v="17"/>
+        <n v="11"/>
+        <n v="21"/>
+        <n v="13"/>
+        <n v="23"/>
+        <n v="27"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Revenue" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="18000" maxValue="350000"/>
@@ -5574,7 +7694,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="352975460"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -5585,480 +7705,480 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="0"/>
     <s v="Arun"/>
-    <n v="5"/>
+    <x v="0"/>
     <n v="250000"/>
     <n v="37500"/>
   </r>
   <r>
     <x v="1"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="1"/>
     <s v="Priya"/>
-    <n v="20"/>
+    <x v="1"/>
     <n v="20000"/>
     <n v="4000"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="2"/>
     <s v="Karthik"/>
-    <n v="15"/>
+    <x v="2"/>
     <n v="22500"/>
     <n v="4500"/>
   </r>
   <r>
     <x v="3"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="3"/>
     <s v="Divya"/>
-    <n v="8"/>
+    <x v="3"/>
     <n v="120000"/>
     <n v="18000"/>
   </r>
   <r>
     <x v="4"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="4"/>
     <s v="Arun"/>
-    <n v="3"/>
+    <x v="4"/>
     <n v="150000"/>
     <n v="22500"/>
   </r>
   <r>
     <x v="5"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="5"/>
     <s v="Priya"/>
-    <n v="25"/>
+    <x v="5"/>
     <n v="25000"/>
     <n v="5000"/>
   </r>
   <r>
     <x v="6"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="Karthik"/>
-    <n v="18"/>
+    <x v="6"/>
     <n v="27000"/>
     <n v="5400"/>
   </r>
   <r>
     <x v="7"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="1"/>
     <s v="Divya"/>
-    <n v="6"/>
+    <x v="7"/>
     <n v="90000"/>
     <n v="13500"/>
   </r>
   <r>
     <x v="8"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="2"/>
     <s v="Arun"/>
-    <n v="4"/>
+    <x v="8"/>
     <n v="200000"/>
     <n v="30000"/>
   </r>
   <r>
     <x v="9"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="3"/>
     <s v="Priya"/>
-    <n v="30"/>
+    <x v="9"/>
     <n v="30000"/>
     <n v="6000"/>
   </r>
   <r>
     <x v="10"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="4"/>
     <s v="Karthik"/>
-    <n v="12"/>
+    <x v="10"/>
     <n v="18000"/>
     <n v="3600"/>
   </r>
   <r>
     <x v="11"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="5"/>
     <s v="Divya"/>
-    <n v="10"/>
+    <x v="11"/>
     <n v="150000"/>
     <n v="22500"/>
   </r>
   <r>
     <x v="12"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="0"/>
     <s v="Arun"/>
-    <n v="6"/>
+    <x v="7"/>
     <n v="300000"/>
     <n v="45000"/>
   </r>
   <r>
     <x v="13"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="1"/>
     <s v="Priya"/>
-    <n v="18"/>
+    <x v="6"/>
     <n v="18000"/>
     <n v="3600"/>
   </r>
   <r>
     <x v="14"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="2"/>
     <s v="Karthik"/>
-    <n v="20"/>
+    <x v="1"/>
     <n v="30000"/>
     <n v="6000"/>
   </r>
   <r>
     <x v="15"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="3"/>
     <s v="Divya"/>
-    <n v="7"/>
+    <x v="12"/>
     <n v="105000"/>
     <n v="15750"/>
   </r>
   <r>
     <x v="16"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="4"/>
     <s v="Arun"/>
-    <n v="5"/>
+    <x v="0"/>
     <n v="250000"/>
     <n v="37500"/>
   </r>
   <r>
     <x v="17"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="5"/>
     <s v="Priya"/>
-    <n v="22"/>
+    <x v="13"/>
     <n v="22000"/>
     <n v="4400"/>
   </r>
   <r>
     <x v="18"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="Karthik"/>
-    <n v="16"/>
+    <x v="14"/>
     <n v="24000"/>
     <n v="4800"/>
   </r>
   <r>
     <x v="19"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="1"/>
     <s v="Divya"/>
-    <n v="9"/>
+    <x v="15"/>
     <n v="135000"/>
     <n v="20250"/>
   </r>
   <r>
     <x v="20"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="2"/>
     <s v="Arun"/>
-    <n v="4"/>
+    <x v="8"/>
     <n v="200000"/>
     <n v="30000"/>
   </r>
   <r>
     <x v="21"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="3"/>
     <s v="Priya"/>
-    <n v="28"/>
+    <x v="16"/>
     <n v="28000"/>
     <n v="5600"/>
   </r>
   <r>
     <x v="22"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="4"/>
     <s v="Karthik"/>
-    <n v="14"/>
+    <x v="17"/>
     <n v="21000"/>
     <n v="4200"/>
   </r>
   <r>
     <x v="23"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="5"/>
     <s v="Divya"/>
-    <n v="8"/>
+    <x v="3"/>
     <n v="120000"/>
     <n v="18000"/>
   </r>
   <r>
     <x v="24"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="0"/>
     <s v="Arun"/>
-    <n v="7"/>
+    <x v="12"/>
     <n v="350000"/>
     <n v="52500"/>
   </r>
   <r>
     <x v="25"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="1"/>
     <s v="Priya"/>
-    <n v="24"/>
+    <x v="18"/>
     <n v="24000"/>
     <n v="4800"/>
   </r>
   <r>
     <x v="26"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="2"/>
     <s v="Karthik"/>
-    <n v="19"/>
+    <x v="19"/>
     <n v="28500"/>
     <n v="5700"/>
   </r>
   <r>
     <x v="27"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="3"/>
     <s v="Divya"/>
-    <n v="5"/>
+    <x v="0"/>
     <n v="75000"/>
     <n v="11250"/>
   </r>
   <r>
     <x v="28"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="4"/>
     <s v="Arun"/>
-    <n v="3"/>
+    <x v="4"/>
     <n v="150000"/>
     <n v="22500"/>
   </r>
   <r>
     <x v="29"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="5"/>
     <s v="Priya"/>
-    <n v="26"/>
+    <x v="20"/>
     <n v="26000"/>
     <n v="5200"/>
   </r>
   <r>
     <x v="30"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="Karthik"/>
-    <n v="17"/>
+    <x v="21"/>
     <n v="25500"/>
     <n v="5100"/>
   </r>
   <r>
     <x v="31"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="1"/>
     <s v="Divya"/>
-    <n v="11"/>
+    <x v="22"/>
     <n v="165000"/>
     <n v="24750"/>
   </r>
   <r>
     <x v="32"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="2"/>
     <s v="Arun"/>
-    <n v="6"/>
+    <x v="7"/>
     <n v="300000"/>
     <n v="45000"/>
   </r>
   <r>
     <x v="33"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="3"/>
     <s v="Priya"/>
-    <n v="21"/>
+    <x v="23"/>
     <n v="21000"/>
     <n v="4200"/>
   </r>
   <r>
     <x v="34"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="4"/>
     <s v="Karthik"/>
-    <n v="13"/>
+    <x v="24"/>
     <n v="19500"/>
     <n v="3900"/>
   </r>
   <r>
     <x v="35"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="5"/>
     <s v="Divya"/>
-    <n v="7"/>
+    <x v="12"/>
     <n v="105000"/>
     <n v="15750"/>
   </r>
   <r>
     <x v="36"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="0"/>
     <s v="Arun"/>
-    <n v="5"/>
+    <x v="0"/>
     <n v="250000"/>
     <n v="37500"/>
   </r>
   <r>
     <x v="37"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="1"/>
     <s v="Priya"/>
-    <n v="23"/>
+    <x v="25"/>
     <n v="23000"/>
     <n v="4600"/>
   </r>
   <r>
     <x v="38"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="2"/>
     <s v="Karthik"/>
-    <n v="16"/>
+    <x v="14"/>
     <n v="24000"/>
     <n v="4800"/>
   </r>
   <r>
     <x v="39"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="3"/>
     <s v="Divya"/>
-    <n v="9"/>
+    <x v="15"/>
     <n v="135000"/>
     <n v="20250"/>
   </r>
   <r>
     <x v="40"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="4"/>
     <s v="Arun"/>
-    <n v="4"/>
+    <x v="8"/>
     <n v="200000"/>
     <n v="30000"/>
   </r>
   <r>
     <x v="41"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="5"/>
     <s v="Priya"/>
-    <n v="27"/>
+    <x v="26"/>
     <n v="27000"/>
     <n v="5400"/>
   </r>
   <r>
     <x v="42"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="Karthik"/>
-    <n v="15"/>
+    <x v="2"/>
     <n v="22500"/>
     <n v="4500"/>
   </r>
   <r>
     <x v="43"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="1"/>
     <s v="Divya"/>
-    <n v="8"/>
+    <x v="3"/>
     <n v="120000"/>
     <n v="18000"/>
   </r>
   <r>
     <x v="44"/>
     <x v="0"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="2"/>
     <s v="Arun"/>
-    <n v="7"/>
+    <x v="12"/>
     <n v="350000"/>
     <n v="52500"/>
   </r>
   <r>
     <x v="45"/>
     <x v="1"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="3"/>
     <s v="Priya"/>
-    <n v="19"/>
+    <x v="19"/>
     <n v="19000"/>
     <n v="3800"/>
   </r>
   <r>
     <x v="46"/>
     <x v="2"/>
-    <s v="Accessories"/>
+    <x v="1"/>
     <x v="4"/>
     <s v="Karthik"/>
-    <n v="18"/>
+    <x v="6"/>
     <n v="27000"/>
     <n v="5400"/>
   </r>
   <r>
     <x v="47"/>
     <x v="3"/>
-    <s v="Electronics"/>
+    <x v="0"/>
     <x v="5"/>
     <s v="Divya"/>
-    <n v="6"/>
+    <x v="7"/>
     <n v="90000"/>
     <n v="13500"/>
   </r>
@@ -6066,7 +8186,283 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B07DA579-76F1-49F4-A4C2-113FB5724E7C}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14" rowHeaderCaption="Date">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B619D55-4DFD-4A59-BE68-67A913755CE4}" name="Revenue by Product" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20" rowHeaderCaption="Product">
+  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Revenue" fld="6" baseField="1" baseItem="0" numFmtId="167"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="187">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="186">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="185">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="184">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="183">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="182">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="19" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{929E7096-91F6-42CE-AB18-C4B98C7CE908}" name="Revenue by Location" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26" rowHeaderCaption="Location">
+  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Revenue" fld="6" baseField="3" baseItem="0" numFmtId="167"/>
+  </dataFields>
+  <formats count="8">
+    <format dxfId="195">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="194">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="193">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="192">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="191">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="190">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="189">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="188">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="8" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="25" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B07DA579-76F1-49F4-A4C2-113FB5724E7C}" name="Daily Revenue Trend" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23" rowHeaderCaption="Date">
   <location ref="D5:E54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0">
@@ -6122,9 +8518,33 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -6286,9 +8706,33 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total Revenue" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Total Revenue" fld="6" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
-  <chartFormats count="1">
+  <formats count="6">
+    <format dxfId="201">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="200">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="199">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="198">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="197">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="196">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
     <chartFormat chart="6" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -6298,8 +8742,26 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="20" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -6311,13 +8773,27 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CFD68984-B044-4A51-8BCB-57E6AE057201}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13" rowHeaderCaption="Location">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CFD68984-B044-4A51-8BCB-57E6AE057201}" name="Profit by Location" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19" rowHeaderCaption="Location">
   <location ref="A27:B34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item x="0"/>
@@ -6364,9 +8840,33 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Total Profit" fld="7" baseField="3" baseItem="0"/>
+    <dataField name="Total Profit" fld="7" baseField="3" baseItem="0" numFmtId="167"/>
   </dataFields>
-  <chartFormats count="1">
+  <formats count="6">
+    <format dxfId="207">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="206">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="205">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="204">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="203">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="202">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
     <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -6376,8 +8876,26 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="16" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -6389,152 +8907,83 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B619D55-4DFD-4A59-BE68-67A913755CE4}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" rowHeaderCaption="Product">
-  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Location" xr10:uid="{C7EF8B75-1699-4560-A6EA-7DDF0188E885}" sourceName="Location">
+  <pivotTables>
+    <pivotTable tabId="4" name="Revenue by Location"/>
+    <pivotTable tabId="4" name="Daily Revenue Trend"/>
+    <pivotTable tabId="4" name="Profit by Location"/>
+    <pivotTable tabId="4" name="Revenue by Product"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="352975460">
+      <items count="6">
+        <i x="0" s="1"/>
+        <i x="4" s="1"/>
+        <i x="2" s="1"/>
+        <i x="5" s="1"/>
+        <i x="3" s="1"/>
+        <i x="1" s="1"/>
       </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Revenue" fld="6" baseField="1" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{929E7096-91F6-42CE-AB18-C4B98C7CE908}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13" rowHeaderCaption="Location">
-  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Category" xr10:uid="{6E75E34F-7CBA-4EA7-B424-4BE0212F0569}" sourceName="Category">
+  <pivotTables>
+    <pivotTable tabId="4" name="Revenue by Product"/>
+    <pivotTable tabId="4" name="Daily Revenue Trend"/>
+    <pivotTable tabId="4" name="Profit by Location"/>
+    <pivotTable tabId="4" name="Revenue by Location"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="352975460">
+      <items count="2">
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
       </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Revenue" fld="6" baseField="3" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="8" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Product" xr10:uid="{CE7676CA-CFA0-4507-83E2-FAEBA0E8EF50}" sourceName="Product">
+  <pivotTables>
+    <pivotTable tabId="4" name="Revenue by Product"/>
+    <pivotTable tabId="4" name="Daily Revenue Trend"/>
+    <pivotTable tabId="4" name="Profit by Location"/>
+    <pivotTable tabId="4" name="Revenue by Location"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="352975460">
+      <items count="4">
+        <i x="2" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="1" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Location 1" xr10:uid="{65253B81-306C-47D1-97FC-E6FF75C6BA5A}" cache="Slicer_Location" caption="Location" rowHeight="247650"/>
+  <slicer name="Category 1" xr10:uid="{3FB5D5DC-9048-409E-A781-CAFC0498329C}" cache="Slicer_Category" caption="Category" rowHeight="247650"/>
+  <slicer name="Product 1" xr10:uid="{389B2EB0-60CA-4116-91BF-850E80EBABA4}" cache="Slicer_Product" caption="Product" rowHeight="247650"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Location" xr10:uid="{D390082E-8E7A-4226-821C-176E763EDEF0}" cache="Slicer_Location" caption="Location" rowHeight="247650"/>
+  <slicer name="Category" xr10:uid="{E38BB5CD-F2C0-441B-897C-C25970CBCFEA}" cache="Slicer_Category" caption="Category" rowHeight="247650"/>
+  <slicer name="Product" xr10:uid="{9F0B4355-A0AC-4873-BCE9-1C9AF2E047AD}" cache="Slicer_Product" caption="Product" rowHeight="247650"/>
+</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8143,7 +10592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8AF74B-E2C7-4E0A-B2EB-8A75244896DF}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
@@ -8158,70 +10607,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39" x14ac:dyDescent="0.75">
-      <c r="A1" s="5"/>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="8" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A4" s="10">
+      <c r="A4" s="6">
         <f>COUNTA('Sales Data'!A2:A51)</f>
         <v>48</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10">
+      <c r="B4" s="5"/>
+      <c r="C4" s="6">
         <f>SUM('Sales Data'!F2:F51)</f>
         <v>629</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="11">
+      <c r="D4" s="5"/>
+      <c r="E4" s="7">
         <f>SUM('Sales Data'!G2:G51)</f>
         <v>4932500</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="11">
+      <c r="F4" s="5"/>
+      <c r="G4" s="7">
         <f>SUM('Sales Data'!H2:H51)</f>
         <v>768500</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="12">
+      <c r="H4" s="5"/>
+      <c r="I4" s="8">
         <f>AVERAGE('Sales Data'!G2:G51)</f>
         <v>102760.41666666667</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="13">
+      <c r="J4" s="5"/>
+      <c r="K4" s="9">
         <f>AVERAGE('Sales Data'!H2:H51)</f>
         <v>16010.416666666666</v>
       </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -8230,564 +10689,575 @@
   <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="B1" s="14"/>
-      <c r="C1" s="10" t="s">
-        <v>79</v>
+      <c r="B1" s="11"/>
+      <c r="C1" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="17">
         <v>1249000</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="10">
         <v>250000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="17">
         <v>835500</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="10">
         <v>165000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="17">
         <v>1155000</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="10">
         <v>20000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="17">
         <v>565000</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="10">
         <v>300000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="17">
         <v>533000</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="10">
         <v>22500</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="17">
         <v>595000</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="10">
         <v>21000</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="10">
         <v>4932500</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="10">
         <v>120000</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="10">
         <v>19500</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="10">
         <v>150000</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="A15" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="10">
         <v>105000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="10">
         <v>25000</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="10">
         <v>250000</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="10">
         <v>289500</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="10">
         <v>27000</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="10">
         <v>2950000</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="10">
         <v>23000</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="10">
         <v>1410000</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="10">
         <v>90000</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="10">
         <v>283000</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="10">
         <v>24000</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="10">
         <v>4932500</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="10">
         <v>200000</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="10">
         <v>135000</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="10">
         <v>30000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="A25" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="10">
         <v>200000</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="10">
         <v>18000</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="10">
         <v>27000</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="10">
         <v>192300</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="10">
         <v>150000</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="10">
         <v>129600</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="10">
         <v>22500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="10">
         <v>178500</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="10">
         <v>300000</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="10">
         <v>89750</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="10">
         <v>120000</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="10">
         <v>84850</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="10">
         <v>18000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="10">
         <v>93500</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="10">
         <v>350000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="10">
         <v>768500</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="10">
         <v>30000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="10">
         <v>19000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="10">
         <v>105000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="10">
         <v>27000</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="10">
         <v>250000</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="10">
         <v>90000</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="10">
         <v>22000</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="10">
         <v>24000</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="10">
         <v>135000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="10">
         <v>200000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="10">
         <v>28000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="10">
         <v>21000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="10">
         <v>120000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="10">
         <v>350000</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="10">
         <v>24000</v>
       </c>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="10">
         <v>28500</v>
       </c>
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="10">
         <v>75000</v>
       </c>
     </row>
     <row r="51" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="10">
         <v>150000</v>
       </c>
     </row>
     <row r="52" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="10">
         <v>26000</v>
       </c>
     </row>
     <row r="53" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="10">
         <v>25500</v>
       </c>
     </row>
     <row r="54" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="10">
         <v>4932500</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId6"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>